--- a/Data/EXCEL/Transfer/salemon/20240711/6839-salemon-20240711.xlsx
+++ b/Data/EXCEL/Transfer/salemon/20240711/6839-salemon-20240711.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlsx\20240711\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\GithubProjects\GoodinfoData2DB\Data\EXCEL\Transfer\salemon\20240711\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{446D3C1A-9809-4014-B142-05F381381AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{99350A14-4ACB-4AF1-BF48-6D3AB05E858D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="290" windowWidth="18240" windowHeight="13390" xr2:uid="{7DE2E339-7FFD-41EF-A0B5-DDA949C1C024}"/>
+    <workbookView xWindow="768" yWindow="684" windowWidth="20004" windowHeight="13956" xr2:uid="{C6447F05-3BA5-41EB-842F-780BCE12F660}"/>
   </bookViews>
   <sheets>
     <sheet name="6839-salemon-20240711" sheetId="2" r:id="rId1"/>
@@ -1261,18 +1261,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A94765B-5C7A-4835-AB34-CFBB38FDF500}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB57CBC0-C330-4D06-A207-66714DC7B58D}">
   <dimension ref="A1:Q81"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="17" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="17" width="5.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1299,7 +1299,7 @@
       <c r="P1" s="19"/>
       <c r="Q1" s="20"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="15" t="s">
         <v>4</v>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -1381,7 +1381,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -1420,7 +1420,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>45444</v>
       </c>
@@ -1473,7 +1473,7 @@
         <v>-40</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>45413</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>-34.299999999999997</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>45383</v>
       </c>
@@ -1579,7 +1579,7 @@
         <v>-33.299999999999997</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <v>45352</v>
       </c>
@@ -1632,7 +1632,7 @@
         <v>-37.4</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>45323</v>
       </c>
@@ -1685,7 +1685,7 @@
         <v>31.9</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <v>45292</v>
       </c>
@@ -1738,7 +1738,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>45261</v>
       </c>
@@ -1791,7 +1791,7 @@
         <v>-44.3</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>45231</v>
       </c>
@@ -1844,7 +1844,7 @@
         <v>-44.7</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>45200</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>-46.7</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
         <v>45170</v>
       </c>
@@ -1950,7 +1950,7 @@
         <v>-46.7</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>45139</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>-48.4</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
         <v>45108</v>
       </c>
@@ -2056,7 +2056,7 @@
         <v>-48.6</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>45078</v>
       </c>
@@ -2109,7 +2109,7 @@
         <v>-49.8</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <v>45047</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>-62.2</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>45017</v>
       </c>
@@ -2215,7 +2215,7 @@
         <v>-64.5</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <v>44986</v>
       </c>
@@ -2268,7 +2268,7 @@
         <v>-58.6</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>44958</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>-73.5</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
         <v>44927</v>
       </c>
@@ -2374,7 +2374,7 @@
         <v>-74.5</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>44896</v>
       </c>
@@ -2427,7 +2427,7 @@
         <v>73.900000000000006</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <v>44866</v>
       </c>
@@ -2480,7 +2480,7 @@
         <v>134.30000000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>44835</v>
       </c>
@@ -2533,7 +2533,7 @@
         <v>150.9</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>44805</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>178.3</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>44774</v>
       </c>
@@ -2639,7 +2639,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>44743</v>
       </c>
@@ -2692,7 +2692,7 @@
         <v>295.60000000000002</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>44713</v>
       </c>
@@ -2745,7 +2745,7 @@
         <v>354.1</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>44682</v>
       </c>
@@ -2798,7 +2798,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>44652</v>
       </c>
@@ -2851,7 +2851,7 @@
         <v>462.6</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>44621</v>
       </c>
@@ -2904,7 +2904,7 @@
         <v>414.8</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>44593</v>
       </c>
@@ -2957,7 +2957,7 @@
         <v>313.10000000000002</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>44562</v>
       </c>
@@ -3010,7 +3010,7 @@
         <v>319.60000000000002</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>44531</v>
       </c>
@@ -3063,7 +3063,7 @@
         <v>-0.05</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="10">
         <v>44501</v>
       </c>
@@ -3116,7 +3116,7 @@
         <v>-21.3</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>44470</v>
       </c>
@@ -3169,7 +3169,7 @@
         <v>-22.3</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>44440</v>
       </c>
@@ -3222,7 +3222,7 @@
         <v>-25.3</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>44409</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>-29.3</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>44378</v>
       </c>
@@ -3328,7 +3328,7 @@
         <v>-9.18</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>44348</v>
       </c>
@@ -3381,202 +3381,202 @@
         <v>7.23</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>45444</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>45413</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>45383</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>45352</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>45323</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>45292</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>45261</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" s="10">
         <v>45231</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>45200</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" s="10">
         <v>45170</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>45139</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" s="10">
         <v>45108</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>45078</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" s="10">
         <v>45047</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>45017</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" s="10">
         <v>44986</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>44958</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" s="10">
         <v>44927</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" s="5">
         <v>44896</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" s="10">
         <v>44866</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" s="5">
         <v>44835</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" s="10">
         <v>44805</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" s="5">
         <v>44774</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" s="10">
         <v>44743</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" s="5">
         <v>44713</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" s="10">
         <v>44682</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" s="5">
         <v>44652</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" s="10">
         <v>44621</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" s="5">
         <v>44593</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" s="10">
         <v>44562</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" s="5">
         <v>44531</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" s="10">
         <v>44501</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" s="5">
         <v>44470</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A77" s="10">
         <v>44440</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78" s="5">
         <v>44409</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" s="10">
         <v>44378</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" s="5">
         <v>44348</v>
       </c>
